--- a/challenge.xlsx
+++ b/challenge.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Documents\UiPath\RPAC2\RPAChallenge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Documents\UiPath\RPAC_2\RPAChallenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B1E64C-8673-41FC-A87E-2EDA4B215291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A271B-F2AC-405D-9247-245FC467C6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
   <si>
     <t>TestCaseNumber</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>TC1</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
@@ -67,12 +64,6 @@
     <t>98 North Road</t>
   </si>
   <si>
-    <t>jsmith@itsolutions.co.uk</t>
-  </si>
-  <si>
-    <t>TC2</t>
-  </si>
-  <si>
     <t>Jane</t>
   </si>
   <si>
@@ -91,9 +82,6 @@
     <t>jdorsey@mc.com</t>
   </si>
   <si>
-    <t>TC3</t>
-  </si>
-  <si>
     <t>Albert</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>kipling@waterfront.com</t>
   </si>
   <si>
-    <t>TC4</t>
-  </si>
-  <si>
     <t>Michael</t>
   </si>
   <si>
@@ -130,9 +115,6 @@
     <t>mrobertson@mc.com</t>
   </si>
   <si>
-    <t>TC5</t>
-  </si>
-  <si>
     <t>Doug</t>
   </si>
   <si>
@@ -148,9 +130,6 @@
     <t>dderrick@timepath.co.uk</t>
   </si>
   <si>
-    <t>TC6</t>
-  </si>
-  <si>
     <t>Jessie</t>
   </si>
   <si>
@@ -169,9 +148,6 @@
     <t>jmarlowe@aperture.us</t>
   </si>
   <si>
-    <t>TC7</t>
-  </si>
-  <si>
     <t>Stan</t>
   </si>
   <si>
@@ -190,9 +166,6 @@
     <t>shamm@sugarwell.org</t>
   </si>
   <si>
-    <t>TC8</t>
-  </si>
-  <si>
     <t>Michelle</t>
   </si>
   <si>
@@ -205,9 +178,6 @@
     <t>mnorton@aperture.us</t>
   </si>
   <si>
-    <t>TC9</t>
-  </si>
-  <si>
     <t>Stacy</t>
   </si>
   <si>
@@ -226,9 +196,6 @@
     <t>sshelby@techdev.com</t>
   </si>
   <si>
-    <t>TC10</t>
-  </si>
-  <si>
     <t>Lara</t>
   </si>
   <si>
@@ -244,7 +211,40 @@
     <t>lpalmer@timepath.co.uk</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>jsmithitsolutions.co.uk</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>TC_1</t>
+  </si>
+  <si>
+    <t>TC_2</t>
+  </si>
+  <si>
+    <t>TC_3</t>
+  </si>
+  <si>
+    <t>TC_4</t>
+  </si>
+  <si>
+    <t>TC_5</t>
+  </si>
+  <si>
+    <t>TC_6</t>
+  </si>
+  <si>
+    <t>TC_7</t>
+  </si>
+  <si>
+    <t>TC_8</t>
+  </si>
+  <si>
+    <t>TC_9</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -673,8 +673,8 @@
     <col min="10" max="27" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -704,54 +704,51 @@
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="H2">
-        <v>407165</v>
-      </c>
-      <c r="I2" t="s">
-        <v>74</v>
+        <v>40781367618</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
       </c>
       <c r="H3">
         <v>40791345621</v>
@@ -759,25 +756,25 @@
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
       </c>
       <c r="H4">
         <v>40735416854</v>
@@ -785,51 +782,54 @@
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
       </c>
       <c r="H5">
         <v>40733652145</v>
+      </c>
+      <c r="I5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <v>40799885412</v>
@@ -837,25 +837,25 @@
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>40733154268</v>
@@ -863,25 +863,25 @@
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H8">
         <v>40712462257</v>
@@ -889,25 +889,25 @@
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H9">
         <v>40731254562</v>
@@ -915,25 +915,25 @@
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H10">
         <v>40741785214</v>
@@ -941,25 +941,25 @@
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H11">
         <v>40731653845</v>
@@ -986,38 +986,46 @@
     <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/challenge.xlsx
+++ b/challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Documents\UiPath\RPAC_2\RPAChallenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A271B-F2AC-405D-9247-245FC467C6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA2D6D4-9E39-4D25-9E8E-465F9CF1BBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>TestCaseNumber</t>
   </si>
@@ -46,205 +46,208 @@
     <t>Phone Number</t>
   </si>
   <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>IT Solutions</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>98 North Road</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Dorsey</t>
+  </si>
+  <si>
+    <t>MediCare</t>
+  </si>
+  <si>
+    <t>Medical Engineer</t>
+  </si>
+  <si>
+    <t>11 Crown Street</t>
+  </si>
+  <si>
+    <t>jdorsey@mc.com</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>Kipling</t>
+  </si>
+  <si>
+    <t>Waterfront</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>22 Guild Street</t>
+  </si>
+  <si>
+    <t>kipling@waterfront.com</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Robertson</t>
+  </si>
+  <si>
+    <t>IT Specialist</t>
+  </si>
+  <si>
+    <t>17 Farburn Terrace</t>
+  </si>
+  <si>
+    <t>mrobertson@mc.com</t>
+  </si>
+  <si>
+    <t>Doug</t>
+  </si>
+  <si>
+    <t>Derrick</t>
+  </si>
+  <si>
+    <t>Timepath Inc.</t>
+  </si>
+  <si>
+    <t>99 Shire Oak Road</t>
+  </si>
+  <si>
+    <t>dderrick@timepath.co.uk</t>
+  </si>
+  <si>
+    <t>Jessie</t>
+  </si>
+  <si>
+    <t>Marlowe</t>
+  </si>
+  <si>
+    <t>Aperture Inc.</t>
+  </si>
+  <si>
+    <t>Scientist</t>
+  </si>
+  <si>
+    <t>27 Cheshire Street</t>
+  </si>
+  <si>
+    <t>jmarlowe@aperture.us</t>
+  </si>
+  <si>
+    <t>Stan</t>
+  </si>
+  <si>
+    <t>Hamm</t>
+  </si>
+  <si>
+    <t>Sugarwell</t>
+  </si>
+  <si>
+    <t>Advisor</t>
+  </si>
+  <si>
+    <t>10 Dam Road</t>
+  </si>
+  <si>
+    <t>shamm@sugarwell.org</t>
+  </si>
+  <si>
+    <t>Michelle</t>
+  </si>
+  <si>
+    <t>Norton</t>
+  </si>
+  <si>
+    <t>13 White Rabbit Street</t>
+  </si>
+  <si>
+    <t>mnorton@aperture.us</t>
+  </si>
+  <si>
+    <t>Stacy</t>
+  </si>
+  <si>
+    <t>Shelby</t>
+  </si>
+  <si>
+    <t>TechDev</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>19 Pineapple Boulevard</t>
+  </si>
+  <si>
+    <t>sshelby@techdev.com</t>
+  </si>
+  <si>
+    <t>Lara</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>Programmer</t>
+  </si>
+  <si>
+    <t>87 Orange Street</t>
+  </si>
+  <si>
+    <t>lpalmer@timepath.co.uk</t>
+  </si>
+  <si>
+    <t>jsmithitsolutions.co.uk</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>TC_1</t>
+  </si>
+  <si>
+    <t>TC_2</t>
+  </si>
+  <si>
+    <t>TC_3</t>
+  </si>
+  <si>
+    <t>TC_4</t>
+  </si>
+  <si>
+    <t>TC_5</t>
+  </si>
+  <si>
+    <t>TC_6</t>
+  </si>
+  <si>
+    <t>TC_7</t>
+  </si>
+  <si>
+    <t>TC_8</t>
+  </si>
+  <si>
+    <t>TC_9</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>IT Solutions</t>
-  </si>
-  <si>
-    <t>Analyst</t>
-  </si>
-  <si>
-    <t>98 North Road</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Dorsey</t>
-  </si>
-  <si>
-    <t>MediCare</t>
-  </si>
-  <si>
-    <t>Medical Engineer</t>
-  </si>
-  <si>
-    <t>11 Crown Street</t>
-  </si>
-  <si>
-    <t>jdorsey@mc.com</t>
-  </si>
-  <si>
-    <t>Albert</t>
-  </si>
-  <si>
-    <t>Kipling</t>
-  </si>
-  <si>
-    <t>Waterfront</t>
-  </si>
-  <si>
-    <t>Accountant</t>
-  </si>
-  <si>
-    <t>22 Guild Street</t>
-  </si>
-  <si>
-    <t>kipling@waterfront.com</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Robertson</t>
-  </si>
-  <si>
-    <t>IT Specialist</t>
-  </si>
-  <si>
-    <t>17 Farburn Terrace</t>
-  </si>
-  <si>
-    <t>mrobertson@mc.com</t>
-  </si>
-  <si>
-    <t>Doug</t>
-  </si>
-  <si>
-    <t>Derrick</t>
-  </si>
-  <si>
-    <t>Timepath Inc.</t>
-  </si>
-  <si>
-    <t>99 Shire Oak Road</t>
-  </si>
-  <si>
-    <t>dderrick@timepath.co.uk</t>
-  </si>
-  <si>
-    <t>Jessie</t>
-  </si>
-  <si>
-    <t>Marlowe</t>
-  </si>
-  <si>
-    <t>Aperture Inc.</t>
-  </si>
-  <si>
-    <t>Scientist</t>
-  </si>
-  <si>
-    <t>27 Cheshire Street</t>
-  </si>
-  <si>
-    <t>jmarlowe@aperture.us</t>
-  </si>
-  <si>
-    <t>Stan</t>
-  </si>
-  <si>
-    <t>Hamm</t>
-  </si>
-  <si>
-    <t>Sugarwell</t>
-  </si>
-  <si>
-    <t>Advisor</t>
-  </si>
-  <si>
-    <t>10 Dam Road</t>
-  </si>
-  <si>
-    <t>shamm@sugarwell.org</t>
-  </si>
-  <si>
-    <t>Michelle</t>
-  </si>
-  <si>
-    <t>Norton</t>
-  </si>
-  <si>
-    <t>13 White Rabbit Street</t>
-  </si>
-  <si>
-    <t>mnorton@aperture.us</t>
-  </si>
-  <si>
-    <t>Stacy</t>
-  </si>
-  <si>
-    <t>Shelby</t>
-  </si>
-  <si>
-    <t>TechDev</t>
-  </si>
-  <si>
-    <t>HR Manager</t>
-  </si>
-  <si>
-    <t>19 Pineapple Boulevard</t>
-  </si>
-  <si>
-    <t>sshelby@techdev.com</t>
-  </si>
-  <si>
-    <t>Lara</t>
-  </si>
-  <si>
-    <t>Palmer</t>
-  </si>
-  <si>
-    <t>Programmer</t>
-  </si>
-  <si>
-    <t>87 Orange Street</t>
-  </si>
-  <si>
-    <t>lpalmer@timepath.co.uk</t>
-  </si>
-  <si>
-    <t>jsmithitsolutions.co.uk</t>
-  </si>
-  <si>
-    <t>TC_10</t>
-  </si>
-  <si>
-    <t>TC_1</t>
-  </si>
-  <si>
-    <t>TC_2</t>
-  </si>
-  <si>
-    <t>TC_3</t>
-  </si>
-  <si>
-    <t>TC_4</t>
-  </si>
-  <si>
-    <t>TC_5</t>
-  </si>
-  <si>
-    <t>TC_6</t>
-  </si>
-  <si>
-    <t>TC_7</t>
-  </si>
-  <si>
-    <t>TC_8</t>
-  </si>
-  <si>
-    <t>TC_9</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
@@ -699,82 +702,88 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2">
         <v>40781367618</v>
+      </c>
+      <c r="I2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
       </c>
       <c r="H3">
         <v>40791345621</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
       </c>
       <c r="H4">
         <v>40735416854</v>
@@ -782,54 +791,51 @@
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
       </c>
       <c r="H5">
         <v>40733652145</v>
-      </c>
-      <c r="I5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
       </c>
       <c r="H6">
         <v>40799885412</v>
@@ -837,51 +843,54 @@
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
       </c>
       <c r="H7">
         <v>40733154268</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
       </c>
       <c r="H8">
         <v>40712462257</v>
@@ -889,25 +898,25 @@
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>50</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
       </c>
       <c r="H9">
         <v>40731254562</v>
@@ -915,25 +924,25 @@
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>55</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>56</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
       </c>
       <c r="H10">
         <v>40741785214</v>
@@ -941,25 +950,25 @@
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>62</v>
       </c>
       <c r="H11">
         <v>40731653845</v>
@@ -996,7 +1005,7 @@
     <row r="40" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1010,7 +1019,7 @@
     <row r="50" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="9:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/challenge.xlsx
+++ b/challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Documents\UiPath\RPAC_2\RPAChallenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA2D6D4-9E39-4D25-9E8E-465F9CF1BBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDB1D90-B1BA-4003-ABB6-A2A8E7D34ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="76">
   <si>
     <t>TestCaseNumber</t>
   </si>
@@ -813,6 +813,9 @@
       </c>
       <c r="H5">
         <v>40733652145</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
